--- a/output/laminas_comunales/comunal_i_ingr_a_2023_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2023_coquimbo.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>11.513947072884</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>9.947885212924445</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>14.27315504135016</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>12.15359586087088</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>13.76747771774036</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>16.93248894924089</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>15.79998233851236</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>11.61838718383059</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,9 +552,6 @@
       <c r="E10">
         <v>14.59701223292575</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -603,9 +571,6 @@
       <c r="E11">
         <v>13.80184157331477</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -625,9 +590,6 @@
       <c r="E12">
         <v>16.48967563036421</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -647,9 +609,6 @@
       <c r="E13">
         <v>14.96303630334523</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -669,9 +628,6 @@
       <c r="E14">
         <v>9.704704910916707</v>
       </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -691,9 +647,6 @@
       <c r="E15">
         <v>16.38688207646142</v>
       </c>
-      <c r="F15" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -712,9 +665,6 @@
       </c>
       <c r="E16">
         <v>15.96524232970631</v>
-      </c>
-      <c r="F16" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_a_2023_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2023_coquimbo.xlsx
@@ -480,191 +480,191 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B7">
-        <v>1080027.5</v>
+        <v>1167796.75</v>
       </c>
       <c r="C7">
-        <v>923633.38</v>
+        <v>1037000.75</v>
       </c>
       <c r="D7">
-        <v>156394.12</v>
+        <v>130796</v>
       </c>
       <c r="E7">
-        <v>16.93248894924089</v>
+        <v>12.61291276790302</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
+          <t>Río Hurtado</t>
         </is>
       </c>
       <c r="B8">
-        <v>1075026.38</v>
+        <v>1080027.5</v>
       </c>
       <c r="C8">
-        <v>928347.62</v>
+        <v>923633.38</v>
       </c>
       <c r="D8">
-        <v>146678.7599999999</v>
+        <v>156394.12</v>
       </c>
       <c r="E8">
-        <v>15.79998233851236</v>
+        <v>16.93248894924089</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
+          <t>Punitaqui</t>
         </is>
       </c>
       <c r="B9">
-        <v>1027944.38</v>
+        <v>1075026.38</v>
       </c>
       <c r="C9">
-        <v>920945.38</v>
+        <v>928347.62</v>
       </c>
       <c r="D9">
-        <v>106999</v>
+        <v>146678.7599999999</v>
       </c>
       <c r="E9">
-        <v>11.61838718383059</v>
+        <v>15.79998233851236</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Canela</t>
+          <t>Los Vilos</t>
         </is>
       </c>
       <c r="B10">
-        <v>1021624.56</v>
+        <v>1027944.38</v>
       </c>
       <c r="C10">
-        <v>891493.1899999999</v>
+        <v>920945.38</v>
       </c>
       <c r="D10">
-        <v>130131.3700000001</v>
+        <v>106999</v>
       </c>
       <c r="E10">
-        <v>14.59701223292575</v>
+        <v>11.61838718383059</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ovalle</t>
+          <t>Canela</t>
         </is>
       </c>
       <c r="B11">
-        <v>1009993.62</v>
+        <v>1021624.56</v>
       </c>
       <c r="C11">
-        <v>887502</v>
+        <v>891493.1899999999</v>
       </c>
       <c r="D11">
-        <v>122491.62</v>
+        <v>130131.3700000001</v>
       </c>
       <c r="E11">
-        <v>13.80184157331477</v>
+        <v>14.59701223292575</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Combarbalá</t>
+          <t>Ovalle</t>
         </is>
       </c>
       <c r="B12">
-        <v>1008543.44</v>
+        <v>1009993.62</v>
       </c>
       <c r="C12">
-        <v>865779.25</v>
+        <v>887502</v>
       </c>
       <c r="D12">
-        <v>142764.1899999999</v>
+        <v>122491.62</v>
       </c>
       <c r="E12">
-        <v>16.48967563036421</v>
+        <v>13.80184157331477</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Vicuña</t>
+          <t>Combarbalá</t>
         </is>
       </c>
       <c r="B13">
-        <v>958072.5600000001</v>
+        <v>1008543.44</v>
       </c>
       <c r="C13">
-        <v>833374.4399999999</v>
+        <v>865779.25</v>
       </c>
       <c r="D13">
-        <v>124698.1200000001</v>
+        <v>142764.1899999999</v>
       </c>
       <c r="E13">
-        <v>14.96303630334523</v>
+        <v>16.48967563036421</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>La Higuera</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="B14">
-        <v>956427.6899999999</v>
+        <v>958072.5600000001</v>
       </c>
       <c r="C14">
-        <v>871820.12</v>
+        <v>833374.4399999999</v>
       </c>
       <c r="D14">
-        <v>84607.56999999995</v>
+        <v>124698.1200000001</v>
       </c>
       <c r="E14">
-        <v>9.704704910916707</v>
+        <v>14.96303630334523</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Monte Patria</t>
+          <t>La Higuera</t>
         </is>
       </c>
       <c r="B15">
-        <v>913079.3100000001</v>
+        <v>956427.6899999999</v>
       </c>
       <c r="C15">
-        <v>784520.8100000001</v>
+        <v>871820.12</v>
       </c>
       <c r="D15">
-        <v>128558.5</v>
+        <v>84607.56999999995</v>
       </c>
       <c r="E15">
-        <v>16.38688207646142</v>
+        <v>9.704704910916707</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Paiguano</t>
+          <t>Monte Patria</t>
         </is>
       </c>
       <c r="B16">
-        <v>911138.1899999999</v>
+        <v>913079.3100000001</v>
       </c>
       <c r="C16">
-        <v>785699.38</v>
+        <v>784520.8100000001</v>
       </c>
       <c r="D16">
-        <v>125438.8099999999</v>
+        <v>128558.5</v>
       </c>
       <c r="E16">
-        <v>15.96524232970631</v>
+        <v>16.38688207646142</v>
       </c>
     </row>
   </sheetData>
@@ -674,7 +674,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -792,50 +792,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paiguano</t>
+          <t>Punitaqui</t>
         </is>
       </c>
       <c r="B12">
-        <v>911138.1899999999</v>
+        <v>1075026.38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
+          <t>Río Hurtado</t>
         </is>
       </c>
       <c r="B13">
-        <v>1075026.38</v>
+        <v>1080027.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="B14">
-        <v>1080027.5</v>
+        <v>1171363.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="B15">
-        <v>1171363.25</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Vicuña</t>
-        </is>
-      </c>
-      <c r="B16">
         <v>958072.5600000001</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_ingr_a_2023_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2023_coquimbo.xlsx
@@ -674,7 +674,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -683,11 +683,6 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -695,138 +690,103 @@
           <t>Andacollo</t>
         </is>
       </c>
-      <c r="B2">
-        <v>1216794.62</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Canela</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>1021624.56</v>
+          <t>Los Vilos</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Combarbalá</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>1008543.44</v>
+          <t>Canela</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>1172608.25</v>
+          <t>Ovalle</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Illapel</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>1175386.75</v>
+          <t>Coquimbo</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>La Higuera</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>956427.6899999999</v>
+          <t>La Serena</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>La Serena</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>1324366.12</v>
+          <t>Combarbalá</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>1027944.38</v>
+          <t>Punitaqui</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Monte Patria</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>913079.3100000001</v>
+          <t>Paihuano</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ovalle</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>1009993.62</v>
+          <t>Illapel</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>1075026.38</v>
+          <t>La Higuera</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>1080027.5</v>
+          <t>Monte Patria</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Salamanca</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>1171363.25</v>
+          <t>Río Hurtado</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Vicuña</t>
         </is>
-      </c>
-      <c r="B15">
-        <v>958072.5600000001</v>
       </c>
     </row>
   </sheetData>
